--- a/00_output/17_retail_rates.xlsx
+++ b/00_output/17_retail_rates.xlsx
@@ -1,80 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/Potential_Study_Tool_Prototype/00_output/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_88BF131C186C96CEEB3B98154BA9AEB8E4AEA9F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6BEB717-D85B-4336-A75C-6F51EC8B7F09}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-3420" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="retail_rates" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="retail_rates" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="8">
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>utility</t>
-  </si>
-  <si>
-    <t>oil_residential_usdperMMBtu</t>
-  </si>
-  <si>
-    <t>natural_gas_residential_usdperMMBtu</t>
-  </si>
-  <si>
-    <t>electric_residential_usdperKWH</t>
-  </si>
-  <si>
-    <t>test_utility_1</t>
-  </si>
-  <si>
-    <t>test_utility_2</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -93,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -395,268 +408,639 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="20" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>oil_residential_usdperMMBtu</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>natural_gas_residential_usdperMMBtu</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>electric_residential_usdperKWH</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>2026</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2026</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>2026</v>
       </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>2027</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>2027</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>2027</v>
       </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>2028</v>
       </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>2028</v>
       </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>2028</v>
       </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>2029</v>
       </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>2029</v>
       </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>2029</v>
       </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>2030</v>
       </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>2030</v>
       </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>2030</v>
       </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>2031</v>
       </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>2031</v>
       </c>
-      <c r="B18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>2031</v>
       </c>
-      <c r="B19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>2032</v>
       </c>
-      <c r="B20" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
         <v>2032</v>
       </c>
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
         <v>2032</v>
       </c>
-      <c r="B22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
         <v>2033</v>
       </c>
-      <c r="B23" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
         <v>2033</v>
       </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>2033</v>
       </c>
-      <c r="B25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
         <v>2034</v>
       </c>
-      <c r="B26" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>2034</v>
       </c>
-      <c r="B27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>2034</v>
       </c>
-      <c r="B28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
         <v>2035</v>
       </c>
-      <c r="B29" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
         <v>2035</v>
       </c>
-      <c r="B30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>2035</v>
       </c>
-      <c r="B31" t="s">
-        <v>7</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2045</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>test_utility_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2045</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2045</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/00_output/17_retail_rates.xlsx
+++ b/00_output/17_retail_rates.xlsx
@@ -459,12 +459,12 @@
   <dimension ref="A1:F181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
